--- a/Master Excel.xlsx
+++ b/Master Excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ODS7493\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB18D326-384B-4D4E-9C94-A6EFB2A88BEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF38F4B-3966-455F-81B0-EBCE8A78AD90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{69292F84-BF6C-44C6-BE65-AA75A0BD03E8}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="147">
   <si>
     <t>Remarks</t>
   </si>
@@ -480,6 +480,9 @@
   </si>
   <si>
     <t>Static ATDT</t>
+  </si>
+  <si>
+    <t>Please update the AZQ app to version v3.2.822.apk specifically for the YouTube test.Kindly note that all other tests must continue to be performed using version v3.2.237.While performing the YouTube test, please ensure that the video is successfully playing in the script before saving the log file</t>
   </si>
 </sst>
 </file>
@@ -1480,7 +1483,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="26" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" ht="39" x14ac:dyDescent="0.35">
       <c r="A17" s="8" t="s">
         <v>85</v>
       </c>
@@ -2929,7 +2932,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:7" ht="53" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B80" s="9" t="s">
         <v>85</v>
       </c>
@@ -2946,7 +2949,7 @@
         <v>102</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>

--- a/Master Excel.xlsx
+++ b/Master Excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ODS7493\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF38F4B-3966-455F-81B0-EBCE8A78AD90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4947AF34-359C-47BE-AAA4-27989DCA683A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{69292F84-BF6C-44C6-BE65-AA75A0BD03E8}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="146">
   <si>
     <t>Remarks</t>
   </si>
@@ -471,9 +471,6 @@
   </si>
   <si>
     <t>While running the scripts, kindly verify in the Events tab that at least 10 websites are browsing. If not, exclude the logfile and create a new one.</t>
-  </si>
-  <si>
-    <t>While performing the YouTube test for both sectors, please ensure that the video is playing successfully in the script before saving the log file.</t>
   </si>
   <si>
     <t>Video Streaming</t>
@@ -1546,7 +1543,7 @@
         <v>24</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G19" s="10" t="s">
         <v>109</v>
@@ -1569,7 +1566,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G20" s="10" t="s">
         <v>108</v>
@@ -1592,7 +1589,7 @@
         <v>26</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G21" s="10" t="s">
         <v>110</v>
@@ -1615,7 +1612,7 @@
         <v>27</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G22" s="10" t="s">
         <v>111</v>
@@ -2627,7 +2624,7 @@
         <v>71</v>
       </c>
       <c r="F66" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G66" s="10" t="s">
         <v>137</v>
@@ -2650,7 +2647,7 @@
         <v>72</v>
       </c>
       <c r="F67" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G67" s="10" t="s">
         <v>88</v>
@@ -2909,7 +2906,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:7" ht="53" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A79" s="8" t="s">
         <v>85</v>
       </c>
@@ -2929,7 +2926,7 @@
         <v>102</v>
       </c>
       <c r="G79" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="53" thickBot="1" x14ac:dyDescent="0.4">
@@ -2943,13 +2940,13 @@
         <v>86</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F80" s="16" t="s">
         <v>102</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/Master Excel.xlsx
+++ b/Master Excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ODS7493\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4947AF34-359C-47BE-AAA4-27989DCA683A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16E74BD6-9A6B-4BF2-8896-2C2D9FA9B066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{69292F84-BF6C-44C6-BE65-AA75A0BD03E8}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="147">
   <si>
     <t>Remarks</t>
   </si>
@@ -480,6 +480,9 @@
   </si>
   <si>
     <t>Please update the AZQ app to version v3.2.822.apk specifically for the YouTube test.Kindly note that all other tests must continue to be performed using version v3.2.237.While performing the YouTube test, please ensure that the video is successfully playing in the script before saving the log file</t>
+  </si>
+  <si>
+    <t>While performing the YouTube test for both sectors, please ensure that the video is playing successfully in the script before saving the log file.</t>
   </si>
 </sst>
 </file>
@@ -2929,7 +2932,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="53" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B80" s="9" t="s">
         <v>85</v>
       </c>
@@ -2946,7 +2949,7 @@
         <v>102</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
